--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.83725793537183</v>
+        <v>9.886054414497924</v>
       </c>
       <c r="D2" t="n">
-        <v>37.24270494845344</v>
+        <v>6.051939554123684</v>
       </c>
       <c r="E2" t="n">
-        <v>6.230922632249712</v>
+        <v>1.012524927740579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.346971148952143</v>
+        <v>0.05638281170472315</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.37541267087241</v>
+        <v>7.861004559016767</v>
       </c>
       <c r="D3" t="n">
-        <v>36.54876265054915</v>
+        <v>5.939173930714237</v>
       </c>
       <c r="E3" t="n">
-        <v>6.230922632249712</v>
+        <v>1.012524927740579</v>
       </c>
       <c r="F3" t="n">
-        <v>0.346971148952143</v>
+        <v>0.05638281170472315</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
